--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ЕМ ЕКС ЕООД/ДЖИ ЕМ ЕКС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ЕМ ЕКС ЕООД/ДЖИ ЕМ ЕКС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,10 +52,16 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-21</t>
   </si>
   <si>
-    <t>Радиново</t>
+    <t>1120 Пловдив Радиново</t>
   </si>
   <si>
     <t>СВ3546КР</t>
@@ -64,7 +73,13 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-21 14:57:03</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>14:56:00</t>
+  </si>
+  <si>
+    <t>3233672785 3233672785</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЖИ ЕМ ЕКС ЕООД</t>
@@ -482,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -491,14 +506,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -532,45 +550,63 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>48.21</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
         <v>1.49</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>71.83</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.57</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>75.69</v>
       </c>
-      <c r="K2" t="s">
-        <v>16</v>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:14">
       <c r="A5" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -578,29 +614,29 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="B7" s="6">
         <v>48.21</v>
@@ -618,9 +654,9 @@
         <v>75.69</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:14">
       <c r="A8" s="8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B8" s="9">
         <v>48.21</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ЕМ ЕКС ЕООД/ДЖИ ЕМ ЕКС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ЕМ ЕКС ЕООД/ДЖИ ЕМ ЕКС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="91">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-01</t>
   </si>
   <si>
@@ -67,10 +73,34 @@
     <t>2026-07-11</t>
   </si>
   <si>
-    <t>Долни Богров</t>
-  </si>
-  <si>
-    <t>София Младост</t>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>1164 София Д. Богров</t>
+  </si>
+  <si>
+    <t>1901 София, Младост 4-ти км</t>
+  </si>
+  <si>
+    <t>1134 Монтана</t>
+  </si>
+  <si>
+    <t>1184 София Дружба2</t>
+  </si>
+  <si>
+    <t>1926 Ботевград</t>
   </si>
   <si>
     <t>СВ8927СХ</t>
@@ -85,6 +115,18 @@
     <t>СВ3546КР</t>
   </si>
   <si>
+    <t>СВ3091РТ</t>
+  </si>
+  <si>
+    <t>СВ1955ТТ</t>
+  </si>
+  <si>
+    <t>СО5803СР</t>
+  </si>
+  <si>
+    <t>M7131BP</t>
+  </si>
+  <si>
     <t>78970152027720193</t>
   </si>
   <si>
@@ -97,31 +139,136 @@
     <t>78970152027720151</t>
   </si>
   <si>
+    <t>78970152027720219</t>
+  </si>
+  <si>
+    <t>78970152027720227</t>
+  </si>
+  <si>
+    <t>78970152027720235</t>
+  </si>
+  <si>
+    <t>78970152027720250</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
     <t>ADBLUE 1L</t>
   </si>
   <si>
-    <t>2026-07-01 15:39:36</t>
-  </si>
-  <si>
-    <t>2026-07-06 18:50:21</t>
-  </si>
-  <si>
-    <t>2026-07-06 18:50:22</t>
-  </si>
-  <si>
-    <t>2026-07-08 13:48:30</t>
-  </si>
-  <si>
-    <t>2026-07-10 06:14:21</t>
-  </si>
-  <si>
-    <t>2026-07-10 06:14:22</t>
-  </si>
-  <si>
-    <t>2026-07-11 11:17:45</t>
+    <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>EKO RACING 100</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>15:37:00</t>
+  </si>
+  <si>
+    <t>18:47:00</t>
+  </si>
+  <si>
+    <t>13:45:00</t>
+  </si>
+  <si>
+    <t>06:11:00</t>
+  </si>
+  <si>
+    <t>11:14:00</t>
+  </si>
+  <si>
+    <t>01:07:00</t>
+  </si>
+  <si>
+    <t>14:56:00</t>
+  </si>
+  <si>
+    <t>18:25:00</t>
+  </si>
+  <si>
+    <t>18:22:00</t>
+  </si>
+  <si>
+    <t>10:06:00</t>
+  </si>
+  <si>
+    <t>08:44:00</t>
+  </si>
+  <si>
+    <t>06:22:00</t>
+  </si>
+  <si>
+    <t>15:10:00</t>
+  </si>
+  <si>
+    <t>15:11:00</t>
+  </si>
+  <si>
+    <t>11:54:00</t>
+  </si>
+  <si>
+    <t>17:55:00</t>
+  </si>
+  <si>
+    <t>17:42:00</t>
+  </si>
+  <si>
+    <t>3234167392 3234167392</t>
+  </si>
+  <si>
+    <t>3234406276 3234406276</t>
+  </si>
+  <si>
+    <t>3234480281 3234480281</t>
+  </si>
+  <si>
+    <t>3234639281 3234639281</t>
+  </si>
+  <si>
+    <t>3234638013 3234638013</t>
+  </si>
+  <si>
+    <t>3234922568 3234922568</t>
+  </si>
+  <si>
+    <t>3234945224 3234945224</t>
+  </si>
+  <si>
+    <t>3235197823 3235197823</t>
+  </si>
+  <si>
+    <t>3235252867 3235252867</t>
+  </si>
+  <si>
+    <t>3235253737 3235253737</t>
+  </si>
+  <si>
+    <t>3235231634 3235231634</t>
+  </si>
+  <si>
+    <t>3235355612 3235355612</t>
+  </si>
+  <si>
+    <t>3235338164 3235338164</t>
+  </si>
+  <si>
+    <t>3235414861 3235414861</t>
+  </si>
+  <si>
+    <t>3235414862 3235414862</t>
+  </si>
+  <si>
+    <t>3235444817 3235444817</t>
+  </si>
+  <si>
+    <t>3235444930 3235444930</t>
+  </si>
+  <si>
+    <t>3235443425 3235443425</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДЖИ ЕМ ЕКС ЕООД</t>
@@ -539,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -548,15 +695,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -593,364 +742,1112 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F2">
         <v>945</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2">
         <v>1.42</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>1341.9</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.51</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>1426.95</v>
       </c>
-      <c r="K2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="L2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F3">
         <v>1202.03</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3">
         <v>1.43</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>1718.9</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.52</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>1827.09</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
         <v>30</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F4">
         <v>56.56</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4">
         <v>1.32</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>74.66</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.32</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>74.66</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
         <v>31</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F5">
         <v>1034.39</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5">
         <v>1.43</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>1479.18</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.52</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>1572.27</v>
       </c>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="L5" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F6">
         <v>955.87</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6">
         <v>1.46</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>1395.57</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.54</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>1472.04</v>
       </c>
-      <c r="K6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="L6" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F7">
         <v>75</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7">
         <v>1.32</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>99</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.32</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>99</v>
       </c>
-      <c r="K7" t="s">
-        <v>34</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="L7" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="F8">
         <v>48.67</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8">
         <v>1.46</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>71.06</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.56</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>75.93000000000001</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9">
+        <v>73.68000000000001</v>
+      </c>
+      <c r="G9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9">
+        <v>1.52</v>
+      </c>
+      <c r="I9" s="1">
+        <v>111.99</v>
+      </c>
+      <c r="J9">
+        <v>1.63</v>
+      </c>
+      <c r="K9" s="1">
+        <v>120.1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10">
+        <v>44.38</v>
+      </c>
+      <c r="G10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10">
+        <v>1.52</v>
+      </c>
+      <c r="I10" s="1">
+        <v>67.45999999999999</v>
+      </c>
+      <c r="J10">
+        <v>1.63</v>
+      </c>
+      <c r="K10" s="1">
+        <v>72.34</v>
+      </c>
+      <c r="L10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11">
+        <v>41.31</v>
+      </c>
+      <c r="G11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11">
+        <v>0.64</v>
+      </c>
+      <c r="I11" s="1">
+        <v>26.44</v>
+      </c>
+      <c r="J11">
+        <v>0.64</v>
+      </c>
+      <c r="K11" s="1">
+        <v>26.44</v>
+      </c>
+      <c r="L11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12">
+        <v>304.62</v>
+      </c>
+      <c r="G12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12">
+        <v>1.61</v>
+      </c>
+      <c r="I12" s="1">
+        <v>490.44</v>
+      </c>
+      <c r="J12">
+        <v>1.7</v>
+      </c>
+      <c r="K12" s="1">
+        <v>517.85</v>
+      </c>
+      <c r="L12" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="G13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13">
+        <v>1.32</v>
+      </c>
+      <c r="I13" s="1">
+        <v>12.92</v>
+      </c>
+      <c r="J13">
+        <v>1.32</v>
+      </c>
+      <c r="K13" s="1">
+        <v>12.92</v>
+      </c>
+      <c r="L13" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14">
+        <v>915.0599999999999</v>
+      </c>
+      <c r="G14" t="s">
+        <v>49</v>
+      </c>
+      <c r="H14">
+        <v>1.61</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1473.25</v>
+      </c>
+      <c r="J14">
+        <v>1.7</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1555.6</v>
+      </c>
+      <c r="L14" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15">
+        <v>20.06</v>
+      </c>
+      <c r="G15" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15">
+        <v>1.81</v>
+      </c>
+      <c r="I15" s="1">
+        <v>36.31</v>
+      </c>
+      <c r="J15">
+        <v>1.81</v>
+      </c>
+      <c r="K15" s="1">
+        <v>36.31</v>
+      </c>
+      <c r="L15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16">
+        <v>960</v>
+      </c>
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16">
+        <v>1.64</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1574.4</v>
+      </c>
+      <c r="J16">
+        <v>1.74</v>
+      </c>
+      <c r="K16" s="1">
+        <v>1670.4</v>
+      </c>
+      <c r="L16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F17">
+        <v>51.99</v>
+      </c>
+      <c r="G17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17">
+        <v>1.32</v>
+      </c>
+      <c r="I17" s="1">
+        <v>68.63</v>
+      </c>
+      <c r="J17">
+        <v>1.32</v>
+      </c>
+      <c r="K17" s="1">
+        <v>68.63</v>
+      </c>
+      <c r="L17" t="s">
+        <v>60</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
         <v>35</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="3" t="s">
+      <c r="D18" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18">
+        <v>44.62</v>
+      </c>
+      <c r="G18" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18">
+        <v>1.64</v>
+      </c>
+      <c r="I18" s="1">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="J18">
+        <v>1.74</v>
+      </c>
+      <c r="K18" s="1">
+        <v>77.64</v>
+      </c>
+      <c r="L18" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18">
+        <v>275000</v>
+      </c>
+      <c r="N18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19">
+        <v>229.06</v>
+      </c>
+      <c r="G19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19">
+        <v>1.64</v>
+      </c>
+      <c r="I19" s="1">
+        <v>375.66</v>
+      </c>
+      <c r="J19">
+        <v>1.75</v>
+      </c>
+      <c r="K19" s="1">
+        <v>400.86</v>
+      </c>
+      <c r="L19" t="s">
+        <v>62</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20">
+        <v>65.36</v>
+      </c>
+      <c r="G20" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20">
+        <v>1.32</v>
+      </c>
+      <c r="I20" s="1">
+        <v>86.28</v>
+      </c>
+      <c r="J20">
+        <v>1.32</v>
+      </c>
+      <c r="K20" s="1">
+        <v>86.28</v>
+      </c>
+      <c r="L20" t="s">
+        <v>63</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21">
+        <v>98.62</v>
+      </c>
+      <c r="G21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21">
+        <v>1.64</v>
+      </c>
+      <c r="I21" s="1">
+        <v>161.74</v>
+      </c>
+      <c r="J21">
+        <v>1.75</v>
+      </c>
+      <c r="K21" s="1">
+        <v>172.58</v>
+      </c>
+      <c r="L21" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F22">
+        <v>35</v>
+      </c>
+      <c r="G22" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22">
+        <v>1.64</v>
+      </c>
+      <c r="I22" s="1">
+        <v>57.4</v>
+      </c>
+      <c r="J22">
+        <v>1.74</v>
+      </c>
+      <c r="K22" s="1">
+        <v>60.9</v>
+      </c>
+      <c r="L22" t="s">
+        <v>65</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="6">
-        <v>4185.96</v>
-      </c>
-      <c r="C13" s="6">
+      <c r="E23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F23">
+        <v>50.85</v>
+      </c>
+      <c r="G23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23">
+        <v>1.64</v>
+      </c>
+      <c r="I23" s="1">
+        <v>83.39</v>
+      </c>
+      <c r="J23">
+        <v>1.75</v>
+      </c>
+      <c r="K23" s="1">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="L23" t="s">
+        <v>66</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="6">
+        <v>6941.85</v>
+      </c>
+      <c r="C28" s="6">
+        <v>15</v>
+      </c>
+      <c r="D28" s="7">
+        <v>1.509</v>
+      </c>
+      <c r="E28" s="6">
+        <v>10475.52</v>
+      </c>
+      <c r="F28" s="6">
+        <v>11111.54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="6">
+        <v>258.7</v>
+      </c>
+      <c r="C29" s="6">
         <v>5</v>
       </c>
-      <c r="D13" s="7">
-        <v>1.4349</v>
-      </c>
-      <c r="E13" s="6">
-        <v>6006.61</v>
-      </c>
-      <c r="F13" s="6">
-        <v>6374.28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="6">
-        <v>131.56</v>
-      </c>
-      <c r="C14" s="6">
-        <v>2</v>
-      </c>
-      <c r="D14" s="7">
+      <c r="D29" s="7">
         <v>1.32</v>
       </c>
-      <c r="E14" s="6">
-        <v>173.66</v>
-      </c>
-      <c r="F14" s="6">
-        <v>173.66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="9">
-        <v>4317.52</v>
-      </c>
-      <c r="C15" s="9">
-        <v>7</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="9">
-        <v>6180.27</v>
-      </c>
-      <c r="F15" s="9">
-        <v>6547.94</v>
+      <c r="E29" s="6">
+        <v>341.49</v>
+      </c>
+      <c r="F29" s="6">
+        <v>341.49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="6">
+        <v>41.31</v>
+      </c>
+      <c r="C30" s="6">
+        <v>1</v>
+      </c>
+      <c r="D30" s="7">
+        <v>0.64</v>
+      </c>
+      <c r="E30" s="6">
+        <v>26.44</v>
+      </c>
+      <c r="F30" s="6">
+        <v>26.44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="6">
+        <v>20.06</v>
+      </c>
+      <c r="C31" s="6">
+        <v>1</v>
+      </c>
+      <c r="D31" s="7">
+        <v>1.8101</v>
+      </c>
+      <c r="E31" s="6">
+        <v>36.31</v>
+      </c>
+      <c r="F31" s="6">
+        <v>36.31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="9">
+        <v>7261.92</v>
+      </c>
+      <c r="C32" s="9">
+        <v>22</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="9">
+        <v>10879.76</v>
+      </c>
+      <c r="F32" s="9">
+        <v>11515.78</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A26:F26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ЕМ ЕКС ЕООД/ДЖИ ЕМ ЕКС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ЕМ ЕКС ЕООД/ДЖИ ЕМ ЕКС ЕООД.xlsx
@@ -295,7 +295,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1758,7 +1758,7 @@
         <v>15</v>
       </c>
       <c r="D28" s="7">
-        <v>1.509</v>
+        <v>1.509039</v>
       </c>
       <c r="E28" s="6">
         <v>10475.52</v>
@@ -1778,7 +1778,7 @@
         <v>5</v>
       </c>
       <c r="D29" s="7">
-        <v>1.32</v>
+        <v>1.320023</v>
       </c>
       <c r="E29" s="6">
         <v>341.49</v>
@@ -1798,7 +1798,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="7">
-        <v>0.64</v>
+        <v>0.640039</v>
       </c>
       <c r="E30" s="6">
         <v>26.44</v>
@@ -1818,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="7">
-        <v>1.8101</v>
+        <v>1.81007</v>
       </c>
       <c r="E31" s="6">
         <v>36.31</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ЕМ ЕКС ЕООД/ДЖИ ЕМ ЕКС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ЕМ ЕКС ЕООД/ДЖИ ЕМ ЕКС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -686,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -699,13 +702,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -748,978 +751,1047 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F2">
         <v>945</v>
       </c>
       <c r="G2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H2">
-        <v>1.42</v>
+        <v>1.399</v>
       </c>
       <c r="I2" s="1">
-        <v>1341.9</v>
+        <v>1.419</v>
       </c>
       <c r="J2">
+        <v>1340.955</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.51</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>1426.95</v>
       </c>
-      <c r="L2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="M2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3">
-        <v>1202.03</v>
+        <v>1202.033</v>
       </c>
       <c r="G3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H3">
-        <v>1.43</v>
+        <v>1.406</v>
       </c>
       <c r="I3" s="1">
-        <v>1718.9</v>
+        <v>1.426</v>
       </c>
       <c r="J3">
+        <v>1714.099058</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.52</v>
       </c>
-      <c r="K3" s="1">
-        <v>1827.09</v>
-      </c>
-      <c r="L3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="L3" s="1">
+        <v>1827.09016</v>
+      </c>
+      <c r="M3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F4">
-        <v>56.56</v>
+        <v>56.561</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H4">
         <v>1.32</v>
       </c>
       <c r="I4" s="1">
-        <v>74.66</v>
+        <v>1.32</v>
       </c>
       <c r="J4">
+        <v>74.66052000000001</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.32</v>
       </c>
-      <c r="K4" s="1">
-        <v>74.66</v>
-      </c>
-      <c r="L4" t="s">
-        <v>51</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="L4" s="1">
+        <v>74.66052000000001</v>
+      </c>
+      <c r="M4" t="s">
+        <v>52</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5">
-        <v>1034.39</v>
+        <v>1034.388</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H5">
-        <v>1.43</v>
+        <v>1.412</v>
       </c>
       <c r="I5" s="1">
-        <v>1479.18</v>
+        <v>1.432</v>
       </c>
       <c r="J5">
+        <v>1481.243616</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.52</v>
       </c>
-      <c r="K5" s="1">
-        <v>1572.27</v>
-      </c>
-      <c r="L5" t="s">
-        <v>52</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="L5" s="1">
+        <v>1572.26976</v>
+      </c>
+      <c r="M5" t="s">
+        <v>53</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F6">
         <v>955.87</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H6">
-        <v>1.46</v>
+        <v>1.437</v>
       </c>
       <c r="I6" s="1">
-        <v>1395.57</v>
+        <v>1.457</v>
       </c>
       <c r="J6">
+        <v>1392.70259</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.54</v>
       </c>
-      <c r="K6" s="1">
-        <v>1472.04</v>
-      </c>
-      <c r="L6" t="s">
-        <v>53</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="L6" s="1">
+        <v>1472.0398</v>
+      </c>
+      <c r="M6" t="s">
+        <v>54</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7">
         <v>75</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H7">
         <v>1.32</v>
       </c>
       <c r="I7" s="1">
+        <v>1.32</v>
+      </c>
+      <c r="J7">
         <v>99</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>1.32</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>99</v>
       </c>
-      <c r="L7" t="s">
-        <v>53</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="M7" t="s">
+        <v>54</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F8">
-        <v>48.67</v>
+        <v>48.673</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H8">
-        <v>1.46</v>
+        <v>1.437</v>
       </c>
       <c r="I8" s="1">
-        <v>71.06</v>
+        <v>1.457</v>
       </c>
       <c r="J8">
+        <v>70.916561</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.56</v>
       </c>
-      <c r="K8" s="1">
-        <v>75.93000000000001</v>
-      </c>
-      <c r="L8" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="L8" s="1">
+        <v>75.92988</v>
+      </c>
+      <c r="M8" t="s">
+        <v>55</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F9">
-        <v>73.68000000000001</v>
+        <v>73.681</v>
       </c>
       <c r="G9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H9">
-        <v>1.52</v>
+        <v>1.499</v>
       </c>
       <c r="I9" s="1">
-        <v>111.99</v>
+        <v>1.519</v>
       </c>
       <c r="J9">
+        <v>111.921439</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.63</v>
       </c>
-      <c r="K9" s="1">
-        <v>120.1</v>
-      </c>
-      <c r="L9" t="s">
-        <v>55</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="L9" s="1">
+        <v>120.10003</v>
+      </c>
+      <c r="M9" t="s">
+        <v>56</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F10">
         <v>44.38</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H10">
-        <v>1.52</v>
+        <v>1.499</v>
       </c>
       <c r="I10" s="1">
-        <v>67.45999999999999</v>
+        <v>1.519</v>
       </c>
       <c r="J10">
+        <v>67.41322</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.63</v>
       </c>
-      <c r="K10" s="1">
-        <v>72.34</v>
-      </c>
-      <c r="L10" t="s">
-        <v>56</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="L10" s="1">
+        <v>72.3394</v>
+      </c>
+      <c r="M10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F11">
-        <v>41.31</v>
+        <v>41.313</v>
       </c>
       <c r="G11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H11">
         <v>0.64</v>
       </c>
       <c r="I11" s="1">
-        <v>26.44</v>
+        <v>0.64</v>
       </c>
       <c r="J11">
+        <v>26.44032</v>
+      </c>
+      <c r="K11" s="1">
         <v>0.64</v>
       </c>
-      <c r="K11" s="1">
-        <v>26.44</v>
-      </c>
-      <c r="L11" t="s">
-        <v>57</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="L11" s="1">
+        <v>26.44032</v>
+      </c>
+      <c r="M11" t="s">
+        <v>58</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F12">
-        <v>304.62</v>
+        <v>304.618</v>
       </c>
       <c r="G12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H12">
-        <v>1.61</v>
+        <v>1.588</v>
       </c>
       <c r="I12" s="1">
-        <v>490.44</v>
+        <v>1.608</v>
       </c>
       <c r="J12">
+        <v>489.825744</v>
+      </c>
+      <c r="K12" s="1">
         <v>1.7</v>
       </c>
-      <c r="K12" s="1">
-        <v>517.85</v>
-      </c>
-      <c r="L12" t="s">
-        <v>58</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="L12" s="1">
+        <v>517.8506</v>
+      </c>
+      <c r="M12" t="s">
+        <v>59</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F13">
-        <v>9.789999999999999</v>
+        <v>9.788</v>
       </c>
       <c r="G13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H13">
         <v>1.32</v>
       </c>
       <c r="I13" s="1">
-        <v>12.92</v>
+        <v>1.32</v>
       </c>
       <c r="J13">
+        <v>12.92016</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.32</v>
       </c>
-      <c r="K13" s="1">
-        <v>12.92</v>
-      </c>
-      <c r="L13" t="s">
-        <v>58</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="L13" s="1">
+        <v>12.92016</v>
+      </c>
+      <c r="M13" t="s">
+        <v>59</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F14">
-        <v>915.0599999999999</v>
+        <v>915.059</v>
       </c>
       <c r="G14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14">
+        <v>1.588</v>
+      </c>
+      <c r="I14" s="1">
+        <v>1.608</v>
+      </c>
+      <c r="J14">
+        <v>1471.414872</v>
+      </c>
+      <c r="K14" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1555.6003</v>
+      </c>
+      <c r="M14" t="s">
+        <v>52</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
         <v>49</v>
       </c>
-      <c r="H14">
-        <v>1.61</v>
-      </c>
-      <c r="I14" s="1">
-        <v>1473.25</v>
-      </c>
-      <c r="J14">
-        <v>1.7</v>
-      </c>
-      <c r="K14" s="1">
-        <v>1555.6</v>
-      </c>
-      <c r="L14" t="s">
-        <v>51</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" t="s">
-        <v>48</v>
-      </c>
       <c r="F15">
-        <v>20.06</v>
+        <v>20.061</v>
       </c>
       <c r="G15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H15">
         <v>1.81</v>
       </c>
       <c r="I15" s="1">
-        <v>36.31</v>
+        <v>1.81</v>
       </c>
       <c r="J15">
+        <v>36.31041</v>
+      </c>
+      <c r="K15" s="1">
         <v>1.81</v>
       </c>
-      <c r="K15" s="1">
-        <v>36.31</v>
-      </c>
-      <c r="L15" t="s">
-        <v>59</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="L15" s="1">
+        <v>36.31041</v>
+      </c>
+      <c r="M15" t="s">
+        <v>60</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16">
         <v>960</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H16">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I16" s="1">
-        <v>1574.4</v>
+        <v>1.639</v>
       </c>
       <c r="J16">
+        <v>1573.44</v>
+      </c>
+      <c r="K16" s="1">
         <v>1.74</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>1670.4</v>
       </c>
-      <c r="L16" t="s">
-        <v>60</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="M16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17">
-        <v>51.99</v>
+        <v>51.992</v>
       </c>
       <c r="G17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H17">
         <v>1.32</v>
       </c>
       <c r="I17" s="1">
-        <v>68.63</v>
+        <v>1.32</v>
       </c>
       <c r="J17">
+        <v>68.62944</v>
+      </c>
+      <c r="K17" s="1">
         <v>1.32</v>
       </c>
-      <c r="K17" s="1">
-        <v>68.63</v>
-      </c>
-      <c r="L17" t="s">
-        <v>60</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="L17" s="1">
+        <v>68.62944</v>
+      </c>
+      <c r="M17" t="s">
+        <v>61</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F18">
-        <v>44.62</v>
+        <v>44.621</v>
       </c>
       <c r="G18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H18">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I18" s="1">
-        <v>73.18000000000001</v>
+        <v>1.639</v>
       </c>
       <c r="J18">
+        <v>73.133819</v>
+      </c>
+      <c r="K18" s="1">
         <v>1.74</v>
       </c>
-      <c r="K18" s="1">
-        <v>77.64</v>
-      </c>
-      <c r="L18" t="s">
-        <v>61</v>
-      </c>
-      <c r="M18">
+      <c r="L18" s="1">
+        <v>77.64054</v>
+      </c>
+      <c r="M18" t="s">
+        <v>62</v>
+      </c>
+      <c r="N18">
         <v>275000</v>
       </c>
-      <c r="N18" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19">
-        <v>229.06</v>
+        <v>229.063</v>
       </c>
       <c r="G19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H19">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I19" s="1">
-        <v>375.66</v>
+        <v>1.639</v>
       </c>
       <c r="J19">
+        <v>375.434257</v>
+      </c>
+      <c r="K19" s="1">
         <v>1.75</v>
       </c>
-      <c r="K19" s="1">
-        <v>400.86</v>
-      </c>
-      <c r="L19" t="s">
-        <v>62</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="L19" s="1">
+        <v>400.86025</v>
+      </c>
+      <c r="M19" t="s">
+        <v>63</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20">
-        <v>65.36</v>
+        <v>65.364</v>
       </c>
       <c r="G20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H20">
         <v>1.32</v>
       </c>
       <c r="I20" s="1">
-        <v>86.28</v>
+        <v>1.32</v>
       </c>
       <c r="J20">
+        <v>86.28048</v>
+      </c>
+      <c r="K20" s="1">
         <v>1.32</v>
       </c>
-      <c r="K20" s="1">
-        <v>86.28</v>
-      </c>
-      <c r="L20" t="s">
-        <v>63</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="L20" s="1">
+        <v>86.28048</v>
+      </c>
+      <c r="M20" t="s">
+        <v>64</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21">
+        <v>98.623</v>
+      </c>
+      <c r="G21" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21">
+        <v>1.619</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1.639</v>
+      </c>
+      <c r="J21">
+        <v>161.643097</v>
+      </c>
+      <c r="K21" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L21" s="1">
+        <v>172.59025</v>
+      </c>
+      <c r="M21" t="s">
+        <v>65</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" t="s">
         <v>24</v>
       </c>
-      <c r="C21" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" t="s">
         <v>45</v>
       </c>
-      <c r="F21">
-        <v>98.62</v>
-      </c>
-      <c r="G21" t="s">
-        <v>49</v>
-      </c>
-      <c r="H21">
-        <v>1.64</v>
-      </c>
-      <c r="I21" s="1">
-        <v>161.74</v>
-      </c>
-      <c r="J21">
-        <v>1.75</v>
-      </c>
-      <c r="K21" s="1">
-        <v>172.58</v>
-      </c>
-      <c r="L21" t="s">
-        <v>64</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" t="s">
-        <v>44</v>
-      </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F22">
         <v>35</v>
       </c>
       <c r="G22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H22">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I22" s="1">
-        <v>57.4</v>
+        <v>1.639</v>
       </c>
       <c r="J22">
+        <v>57.365</v>
+      </c>
+      <c r="K22" s="1">
         <v>1.74</v>
       </c>
-      <c r="K22" s="1">
+      <c r="L22" s="1">
         <v>60.9</v>
       </c>
-      <c r="L22" t="s">
-        <v>65</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="M22" t="s">
+        <v>66</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F23">
-        <v>50.85</v>
+        <v>50.851</v>
       </c>
       <c r="G23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H23">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I23" s="1">
-        <v>83.39</v>
+        <v>1.639</v>
       </c>
       <c r="J23">
+        <v>83.34478900000001</v>
+      </c>
+      <c r="K23" s="1">
         <v>1.75</v>
       </c>
-      <c r="K23" s="1">
-        <v>88.98999999999999</v>
-      </c>
-      <c r="L23" t="s">
-        <v>66</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="L23" s="1">
+        <v>88.98925</v>
+      </c>
+      <c r="M23" t="s">
+        <v>67</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -1727,58 +1799,58 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:15">
       <c r="A27" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B28" s="6">
-        <v>6941.85</v>
+        <v>6941.86</v>
       </c>
       <c r="C28" s="6">
         <v>15</v>
       </c>
       <c r="D28" s="7">
-        <v>1.509039</v>
+        <v>1.5075</v>
       </c>
       <c r="E28" s="6">
-        <v>10475.52</v>
+        <v>10464.85</v>
       </c>
       <c r="F28" s="6">
-        <v>11111.54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+        <v>11111.55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B29" s="6">
-        <v>258.7</v>
+        <v>258.705</v>
       </c>
       <c r="C29" s="6">
         <v>5</v>
       </c>
       <c r="D29" s="7">
-        <v>1.320023</v>
+        <v>1.32</v>
       </c>
       <c r="E29" s="6">
         <v>341.49</v>
@@ -1787,18 +1859,18 @@
         <v>341.49</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:15">
       <c r="A30" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B30" s="6">
-        <v>41.31</v>
+        <v>41.313</v>
       </c>
       <c r="C30" s="6">
         <v>1</v>
       </c>
       <c r="D30" s="7">
-        <v>0.640039</v>
+        <v>0.64</v>
       </c>
       <c r="E30" s="6">
         <v>26.44</v>
@@ -1807,18 +1879,18 @@
         <v>26.44</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:15">
       <c r="A31" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B31" s="6">
-        <v>20.06</v>
+        <v>20.061</v>
       </c>
       <c r="C31" s="6">
         <v>1</v>
       </c>
       <c r="D31" s="7">
-        <v>1.81007</v>
+        <v>1.81</v>
       </c>
       <c r="E31" s="6">
         <v>36.31</v>
@@ -1827,22 +1899,22 @@
         <v>36.31</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:15">
       <c r="A32" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B32" s="9">
-        <v>7261.92</v>
+        <v>7261.939</v>
       </c>
       <c r="C32" s="9">
         <v>22</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="9">
-        <v>10879.76</v>
+        <v>10869.09</v>
       </c>
       <c r="F32" s="9">
-        <v>11515.78</v>
+        <v>11515.79</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ЕМ ЕКС ЕООД/ДЖИ ЕМ ЕКС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДЖИ ЕМ ЕКС ЕООД/ДЖИ ЕМ ЕКС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="91">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -297,8 +294,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -391,10 +388,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -689,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -702,13 +699,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -751,1047 +748,978 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F2">
         <v>945</v>
       </c>
       <c r="G2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2">
+        <v>1.419</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1340.955</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1426.95</v>
+      </c>
+      <c r="L2" t="s">
         <v>50</v>
       </c>
-      <c r="H2">
-        <v>1.399</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.419</v>
-      </c>
-      <c r="J2">
-        <v>1340.955</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>1426.95</v>
-      </c>
-      <c r="M2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F3">
         <v>1202.033</v>
       </c>
       <c r="G3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H3">
-        <v>1.406</v>
+        <v>1.426</v>
       </c>
       <c r="I3" s="1">
-        <v>1.426</v>
+        <v>1714.099</v>
       </c>
       <c r="J3">
-        <v>1714.099058</v>
+        <v>1.52</v>
       </c>
       <c r="K3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L3" s="1">
-        <v>1827.09016</v>
-      </c>
-      <c r="M3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>1827.09</v>
+      </c>
+      <c r="L3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F4">
         <v>56.561</v>
       </c>
       <c r="G4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H4">
         <v>1.32</v>
       </c>
       <c r="I4" s="1">
+        <v>74.661</v>
+      </c>
+      <c r="J4">
         <v>1.32</v>
       </c>
-      <c r="J4">
-        <v>74.66052000000001</v>
-      </c>
       <c r="K4" s="1">
-        <v>1.32</v>
-      </c>
-      <c r="L4" s="1">
-        <v>74.66052000000001</v>
-      </c>
-      <c r="M4" t="s">
-        <v>52</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+        <v>74.661</v>
+      </c>
+      <c r="L4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F5">
         <v>1034.388</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H5">
-        <v>1.412</v>
+        <v>1.432</v>
       </c>
       <c r="I5" s="1">
-        <v>1.432</v>
+        <v>1481.244</v>
       </c>
       <c r="J5">
-        <v>1481.243616</v>
+        <v>1.52</v>
       </c>
       <c r="K5" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1572.26976</v>
-      </c>
-      <c r="M5" t="s">
-        <v>53</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>1572.27</v>
+      </c>
+      <c r="L5" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6">
         <v>955.87</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H6">
-        <v>1.437</v>
+        <v>1.457</v>
       </c>
       <c r="I6" s="1">
-        <v>1.457</v>
+        <v>1392.703</v>
       </c>
       <c r="J6">
-        <v>1392.70259</v>
+        <v>1.54</v>
       </c>
       <c r="K6" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L6" s="1">
-        <v>1472.0398</v>
-      </c>
-      <c r="M6" t="s">
-        <v>54</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>1472.04</v>
+      </c>
+      <c r="L6" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F7">
         <v>75</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H7">
         <v>1.32</v>
       </c>
       <c r="I7" s="1">
+        <v>99</v>
+      </c>
+      <c r="J7">
         <v>1.32</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>99</v>
       </c>
-      <c r="K7" s="1">
-        <v>1.32</v>
-      </c>
-      <c r="L7" s="1">
-        <v>99</v>
-      </c>
-      <c r="M7" t="s">
-        <v>54</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="L7" t="s">
+        <v>53</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F8">
         <v>48.673</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H8">
-        <v>1.437</v>
+        <v>1.457</v>
       </c>
       <c r="I8" s="1">
-        <v>1.457</v>
+        <v>70.917</v>
       </c>
       <c r="J8">
-        <v>70.916561</v>
+        <v>1.56</v>
       </c>
       <c r="K8" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L8" s="1">
-        <v>75.92988</v>
-      </c>
-      <c r="M8" t="s">
-        <v>55</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>75.93000000000001</v>
+      </c>
+      <c r="L8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F9">
         <v>73.681</v>
       </c>
       <c r="G9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H9">
-        <v>1.499</v>
+        <v>1.519</v>
       </c>
       <c r="I9" s="1">
-        <v>1.519</v>
+        <v>111.921</v>
       </c>
       <c r="J9">
-        <v>111.921439</v>
+        <v>1.63</v>
       </c>
       <c r="K9" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L9" s="1">
-        <v>120.10003</v>
-      </c>
-      <c r="M9" t="s">
-        <v>56</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+        <v>120.1</v>
+      </c>
+      <c r="L9" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F10">
         <v>44.38</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H10">
-        <v>1.499</v>
+        <v>1.519</v>
       </c>
       <c r="I10" s="1">
-        <v>1.519</v>
+        <v>67.413</v>
       </c>
       <c r="J10">
-        <v>67.41322</v>
+        <v>1.63</v>
       </c>
       <c r="K10" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L10" s="1">
-        <v>72.3394</v>
-      </c>
-      <c r="M10" t="s">
-        <v>57</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+        <v>72.339</v>
+      </c>
+      <c r="L10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11">
         <v>41.313</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H11">
         <v>0.64</v>
       </c>
       <c r="I11" s="1">
+        <v>26.44</v>
+      </c>
+      <c r="J11">
         <v>0.64</v>
       </c>
-      <c r="J11">
-        <v>26.44032</v>
-      </c>
       <c r="K11" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L11" s="1">
-        <v>26.44032</v>
-      </c>
-      <c r="M11" t="s">
-        <v>58</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>26.44</v>
+      </c>
+      <c r="L11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F12">
         <v>304.618</v>
       </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H12">
-        <v>1.588</v>
+        <v>1.608</v>
       </c>
       <c r="I12" s="1">
-        <v>1.608</v>
+        <v>489.826</v>
       </c>
       <c r="J12">
-        <v>489.825744</v>
+        <v>1.7</v>
       </c>
       <c r="K12" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L12" s="1">
-        <v>517.8506</v>
-      </c>
-      <c r="M12" t="s">
-        <v>59</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>517.851</v>
+      </c>
+      <c r="L12" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13">
         <v>9.788</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H13">
         <v>1.32</v>
       </c>
       <c r="I13" s="1">
+        <v>12.92</v>
+      </c>
+      <c r="J13">
         <v>1.32</v>
       </c>
-      <c r="J13">
-        <v>12.92016</v>
-      </c>
       <c r="K13" s="1">
-        <v>1.32</v>
-      </c>
-      <c r="L13" s="1">
-        <v>12.92016</v>
-      </c>
-      <c r="M13" t="s">
-        <v>59</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>12.92</v>
+      </c>
+      <c r="L13" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F14">
         <v>915.059</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H14">
-        <v>1.588</v>
+        <v>1.608</v>
       </c>
       <c r="I14" s="1">
-        <v>1.608</v>
+        <v>1471.415</v>
       </c>
       <c r="J14">
-        <v>1471.414872</v>
+        <v>1.7</v>
       </c>
       <c r="K14" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L14" s="1">
-        <v>1555.6003</v>
-      </c>
-      <c r="M14" t="s">
-        <v>52</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>1555.6</v>
+      </c>
+      <c r="L14" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F15">
         <v>20.061</v>
       </c>
       <c r="G15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H15">
         <v>1.81</v>
       </c>
       <c r="I15" s="1">
+        <v>36.31</v>
+      </c>
+      <c r="J15">
         <v>1.81</v>
       </c>
-      <c r="J15">
-        <v>36.31041</v>
-      </c>
       <c r="K15" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="L15" s="1">
-        <v>36.31041</v>
-      </c>
-      <c r="M15" t="s">
-        <v>60</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>36.31</v>
+      </c>
+      <c r="L15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F16">
         <v>960</v>
       </c>
       <c r="G16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H16">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I16" s="1">
-        <v>1.639</v>
+        <v>1573.44</v>
       </c>
       <c r="J16">
-        <v>1573.44</v>
+        <v>1.74</v>
       </c>
       <c r="K16" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L16" s="1">
         <v>1670.4</v>
       </c>
-      <c r="M16" t="s">
-        <v>61</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="L16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F17">
         <v>51.992</v>
       </c>
       <c r="G17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H17">
         <v>1.32</v>
       </c>
       <c r="I17" s="1">
+        <v>68.629</v>
+      </c>
+      <c r="J17">
         <v>1.32</v>
       </c>
-      <c r="J17">
-        <v>68.62944</v>
-      </c>
       <c r="K17" s="1">
-        <v>1.32</v>
-      </c>
-      <c r="L17" s="1">
-        <v>68.62944</v>
-      </c>
-      <c r="M17" t="s">
-        <v>61</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>68.629</v>
+      </c>
+      <c r="L17" t="s">
+        <v>60</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F18">
         <v>44.621</v>
       </c>
       <c r="G18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H18">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I18" s="1">
-        <v>1.639</v>
+        <v>73.134</v>
       </c>
       <c r="J18">
-        <v>73.133819</v>
+        <v>1.74</v>
       </c>
       <c r="K18" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L18" s="1">
-        <v>77.64054</v>
-      </c>
-      <c r="M18" t="s">
-        <v>62</v>
-      </c>
-      <c r="N18">
+        <v>77.64100000000001</v>
+      </c>
+      <c r="L18" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18">
         <v>275000</v>
       </c>
-      <c r="O18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="N18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F19">
         <v>229.063</v>
       </c>
       <c r="G19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H19">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I19" s="1">
-        <v>1.639</v>
+        <v>375.434</v>
       </c>
       <c r="J19">
-        <v>375.434257</v>
+        <v>1.75</v>
       </c>
       <c r="K19" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L19" s="1">
-        <v>400.86025</v>
-      </c>
-      <c r="M19" t="s">
-        <v>63</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>400.86</v>
+      </c>
+      <c r="L19" t="s">
+        <v>62</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F20">
         <v>65.364</v>
       </c>
       <c r="G20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H20">
         <v>1.32</v>
       </c>
       <c r="I20" s="1">
+        <v>86.28</v>
+      </c>
+      <c r="J20">
         <v>1.32</v>
       </c>
-      <c r="J20">
-        <v>86.28048</v>
-      </c>
       <c r="K20" s="1">
-        <v>1.32</v>
-      </c>
-      <c r="L20" s="1">
-        <v>86.28048</v>
-      </c>
-      <c r="M20" t="s">
-        <v>64</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+        <v>86.28</v>
+      </c>
+      <c r="L20" t="s">
+        <v>63</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
         <v>24</v>
       </c>
-      <c r="B21" t="s">
-        <v>25</v>
-      </c>
       <c r="C21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F21">
         <v>98.623</v>
       </c>
       <c r="G21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H21">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I21" s="1">
-        <v>1.639</v>
+        <v>161.643</v>
       </c>
       <c r="J21">
-        <v>161.643097</v>
+        <v>1.75</v>
       </c>
       <c r="K21" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L21" s="1">
-        <v>172.59025</v>
-      </c>
-      <c r="M21" t="s">
-        <v>65</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>172.59</v>
+      </c>
+      <c r="L21" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" t="s">
         <v>45</v>
-      </c>
-      <c r="E22" t="s">
-        <v>46</v>
       </c>
       <c r="F22">
         <v>35</v>
       </c>
       <c r="G22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H22">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I22" s="1">
-        <v>1.639</v>
+        <v>57.365</v>
       </c>
       <c r="J22">
-        <v>57.365</v>
+        <v>1.74</v>
       </c>
       <c r="K22" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L22" s="1">
         <v>60.9</v>
       </c>
-      <c r="M22" t="s">
-        <v>66</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+      <c r="L22" t="s">
+        <v>65</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F23">
         <v>50.851</v>
       </c>
       <c r="G23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H23">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I23" s="1">
-        <v>1.639</v>
+        <v>83.345</v>
       </c>
       <c r="J23">
-        <v>83.34478900000001</v>
+        <v>1.75</v>
       </c>
       <c r="K23" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L23" s="1">
-        <v>88.98925</v>
-      </c>
-      <c r="M23" t="s">
-        <v>67</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
+        <v>88.989</v>
+      </c>
+      <c r="L23" t="s">
+        <v>66</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="3" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
-      <c r="A26" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -1799,109 +1727,109 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:14">
       <c r="A27" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="E27" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B28" s="6">
         <v>6941.86</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="7">
         <v>15</v>
       </c>
       <c r="D28" s="7">
-        <v>1.5075</v>
-      </c>
-      <c r="E28" s="6">
-        <v>10464.85</v>
-      </c>
-      <c r="F28" s="6">
+        <v>1.508</v>
+      </c>
+      <c r="E28" s="7">
+        <v>10464.854</v>
+      </c>
+      <c r="F28" s="7">
         <v>11111.55</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:14">
       <c r="A29" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B29" s="6">
         <v>258.705</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="7">
         <v>5</v>
       </c>
       <c r="D29" s="7">
         <v>1.32</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="7">
         <v>341.49</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="7">
         <v>341.49</v>
       </c>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:14">
       <c r="A30" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B30" s="6">
         <v>41.313</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="7">
         <v>1</v>
       </c>
       <c r="D30" s="7">
         <v>0.64</v>
       </c>
-      <c r="E30" s="6">
+      <c r="E30" s="7">
         <v>26.44</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="7">
         <v>26.44</v>
       </c>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:14">
       <c r="A31" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B31" s="6">
         <v>20.061</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="7">
         <v>1</v>
       </c>
       <c r="D31" s="7">
         <v>1.81</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="7">
         <v>36.31</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="7">
         <v>36.31</v>
       </c>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:14">
       <c r="A32" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B32" s="9">
         <v>7261.939</v>
@@ -1911,7 +1839,7 @@
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="9">
-        <v>10869.09</v>
+        <v>10869.094</v>
       </c>
       <c r="F32" s="9">
         <v>11515.79</v>
